--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MARQUEZ</t>
+  </si>
+  <si>
+    <t>TIZA</t>
+  </si>
+  <si>
+    <t>CRISTIAN OSMAR</t>
   </si>
 </sst>
 </file>
@@ -530,16 +539,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="E2">
-        <v>28</v>
+        <v>6</v>
       </c>
       <c r="F2">
-        <v>0</v>
+        <v>22</v>
       </c>
       <c r="G2">
-        <v>0</v>
+        <v>56.41</v>
+      </c>
+      <c r="H2">
+        <v>9.300000000000001</v>
       </c>
     </row>
   </sheetData>
@@ -604,7 +616,7 @@
         <v>71.79000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>9.199999999999999</v>
       </c>
     </row>
   </sheetData>
@@ -614,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -644,6 +656,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>22330051920359</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
   <si>
     <t>Mat</t>
   </si>
@@ -65,15 +65,6 @@
   </si>
   <si>
     <t>Reprobadas</t>
-  </si>
-  <si>
-    <t>MARQUEZ</t>
-  </si>
-  <si>
-    <t>TIZA</t>
-  </si>
-  <si>
-    <t>CRISTIAN OSMAR</t>
   </si>
 </sst>
 </file>
@@ -626,7 +617,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G2"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -656,29 +647,6 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2">
-        <v>22330051920359</v>
-      </c>
-      <c r="B2" t="s">
-        <v>16</v>
-      </c>
-      <c r="C2" t="s">
-        <v>17</v>
-      </c>
-      <c r="D2" t="s">
-        <v>18</v>
-      </c>
-      <c r="E2" t="s">
-        <v>8</v>
-      </c>
-      <c r="F2" t="s">
-        <v>9</v>
-      </c>
-      <c r="G2">
-        <v>2</v>
-      </c>
-    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -530,16 +530,16 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="E2">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>22</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>56.41</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
         <v>9.300000000000001</v>
@@ -607,7 +607,7 @@
         <v>71.79000000000001</v>
       </c>
       <c r="H2">
-        <v>9.199999999999999</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -530,7 +530,7 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="E2">
         <v>1</v>
@@ -542,7 +542,7 @@
         <v>69.23</v>
       </c>
       <c r="H2">
-        <v>9.300000000000001</v>
+        <v>9.1</v>
       </c>
     </row>
   </sheetData>
@@ -598,13 +598,13 @@
         <v>11</v>
       </c>
       <c r="E2">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F2">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="G2">
-        <v>71.79000000000001</v>
+        <v>69.23</v>
       </c>
       <c r="H2">
         <v>9.1</v>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -465,10 +465,10 @@
         <v>39</v>
       </c>
       <c r="D2">
+        <v>0</v>
+      </c>
+      <c r="E2">
         <v>11</v>
-      </c>
-      <c r="E2">
-        <v>0</v>
       </c>
       <c r="F2">
         <v>28</v>
@@ -477,7 +477,7 @@
         <v>71.79000000000001</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -530,19 +530,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>69.23</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -595,19 +595,19 @@
         <v>39</v>
       </c>
       <c r="D2">
-        <v>11</v>
+        <v>0</v>
       </c>
       <c r="E2">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="F2">
-        <v>27</v>
+        <v>35</v>
       </c>
       <c r="G2">
-        <v>69.23</v>
+        <v>89.73999999999999</v>
       </c>
       <c r="H2">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
     </row>
   </sheetData>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -17,7 +17,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="37" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="42" uniqueCount="19">
   <si>
     <t>Mat</t>
   </si>
@@ -65,6 +65,15 @@
   </si>
   <si>
     <t>Reprobadas</t>
+  </si>
+  <si>
+    <t>MARTINEZ</t>
+  </si>
+  <si>
+    <t>GARCIA</t>
+  </si>
+  <si>
+    <t>RICARDO ABEL</t>
   </si>
 </sst>
 </file>
@@ -617,7 +626,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:G2"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <cols>
     <col min="1" max="4" width="15.7109375" customWidth="1"/>
@@ -647,6 +656,29 @@
         <v>15</v>
       </c>
     </row>
+    <row r="2" spans="1:7">
+      <c r="A2">
+        <v>21330051920265</v>
+      </c>
+      <c r="B2" t="s">
+        <v>16</v>
+      </c>
+      <c r="C2" t="s">
+        <v>17</v>
+      </c>
+      <c r="D2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E2" t="s">
+        <v>8</v>
+      </c>
+      <c r="F2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2">
+        <v>2</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
+++ b/docentes/Saucedo Rivalcoba Graciela - Estadisticos 20221.xlsx
@@ -607,13 +607,13 @@
         <v>0</v>
       </c>
       <c r="E2">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="F2">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="G2">
-        <v>89.73999999999999</v>
+        <v>92.31</v>
       </c>
       <c r="H2">
         <v>8.300000000000001</v>
